--- a/artfynd/A 38335-2023 artfynd.xlsx
+++ b/artfynd/A 38335-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129721919</v>
       </c>
       <c r="B2" t="n">
-        <v>57839</v>
+        <v>57840</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129722015</v>
       </c>
       <c r="B3" t="n">
-        <v>58368</v>
+        <v>58369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129727154</v>
       </c>
       <c r="B4" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>129726970</v>
       </c>
       <c r="B5" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38335-2023 artfynd.xlsx
+++ b/artfynd/A 38335-2023 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>129726970</v>
       </c>
       <c r="B5" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38335-2023 artfynd.xlsx
+++ b/artfynd/A 38335-2023 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>129726970</v>
       </c>
       <c r="B5" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38335-2023 artfynd.xlsx
+++ b/artfynd/A 38335-2023 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>129726970</v>
       </c>
       <c r="B5" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38335-2023 artfynd.xlsx
+++ b/artfynd/A 38335-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129721919</v>
       </c>
       <c r="B2" t="n">
-        <v>57840</v>
+        <v>57841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129722015</v>
       </c>
       <c r="B3" t="n">
-        <v>58369</v>
+        <v>58372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129727154</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>129726970</v>
       </c>
       <c r="B5" t="n">
-        <v>91897</v>
+        <v>91900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38335-2023 artfynd.xlsx
+++ b/artfynd/A 38335-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,62 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129721919</v>
+        <v>129726970</v>
       </c>
       <c r="B2" t="n">
-        <v>57844</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Trångbodarna, Trångbodarna, Jmt</t>
+          <t>Grötomsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>501667</v>
+        <v>501509</v>
       </c>
       <c r="R2" t="n">
-        <v>7037322</v>
+        <v>7037075</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,73 +770,84 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Eriksson</t>
+          <t>Bo Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Eriksson</t>
+          <t>Bo Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129722015</v>
+        <v>120711070</v>
       </c>
       <c r="B3" t="n">
-        <v>58376</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102125</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Häståken, Häståken, Jmt</t>
+          <t>Trångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501667</v>
+        <v>501583</v>
       </c>
       <c r="R3" t="n">
-        <v>7037322</v>
+        <v>7037272</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,12 +871,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2024-10-27</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2024-10-27</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,48 +913,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129727154</v>
+        <v>121213493</v>
       </c>
       <c r="B4" t="n">
-        <v>57740</v>
+        <v>91923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grötomsbodarna, Jmt</t>
+          <t>Trångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501428</v>
+        <v>501583</v>
       </c>
       <c r="R4" t="n">
-        <v>7037099</v>
+        <v>7037272</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -952,17 +978,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spår av födosök, barkflagor</t>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -973,93 +1004,64 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo Persson</t>
+          <t>Andreas Eriksson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo Persson</t>
+          <t>Andreas Eriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129726970</v>
+        <v>121101152</v>
       </c>
       <c r="B5" t="n">
-        <v>91926</v>
+        <v>92632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Grötomsbodarna, Jmt</t>
+          <t>Trångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501509</v>
+        <v>501583</v>
       </c>
       <c r="R5" t="n">
-        <v>7037075</v>
+        <v>7037272</v>
       </c>
       <c r="S5" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,12 +1085,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,39 +1111,795 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Andreas Eriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Andreas Eriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>119480526</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Trångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>501583</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7037272</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Andreas Eriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Andreas Eriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129727154</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Grötomsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>501428</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7037099</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Spår av födosök, barkflagor</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Bo Persson</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Bo Persson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129722015</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58592</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102125</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tallbit</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pinicola enucleator</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Häståken, Häståken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>501667</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7037322</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Andreas Eriksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Andreas Eriksson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>119483293</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äggskal</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Trångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>501583</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7037272</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Andreas Eriksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Andreas Eriksson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120381974</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Trångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>501583</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7037272</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Andreas Eriksson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Andreas Eriksson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>104839580</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Trångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>501583</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7037272</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-11-27</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-11-27</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Andreas Eriksson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Andreas Eriksson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129721919</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Trångbodarna, Trångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>501667</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7037322</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Andreas Eriksson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Andreas Eriksson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38335-2023 artfynd.xlsx
+++ b/artfynd/A 38335-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -803,6 +808,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129726970</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120711070</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121213493</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121101152</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1231,6 +1256,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480526</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,6 +1378,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129727154</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1454,6 +1489,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129722015</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1566,6 +1606,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119483293</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1682,6 +1727,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120381974</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1794,6 +1844,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104839580</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1900,8 +1955,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129721919</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>